--- a/Result/profitability/3260.xlsx
+++ b/Result/profitability/3260.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-3.12</v>
       </c>
       <c r="M2" t="n">
-        <v>6.6425</v>
+        <v>10.44</v>
       </c>
       <c r="N2" t="n">
-        <v>24.58625</v>
+        <v>27.17375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.32</v>
       </c>
       <c r="M3" t="n">
-        <v>6.226249999999999</v>
+        <v>10.145</v>
       </c>
       <c r="N3" t="n">
-        <v>22.06625</v>
+        <v>25.595</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-2.71</v>
       </c>
       <c r="M4" t="n">
-        <v>5.757499999999999</v>
+        <v>9.59125</v>
       </c>
       <c r="N4" t="n">
-        <v>20.3925</v>
+        <v>23.935</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-5.08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9075</v>
+        <v>8.612500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>17.67125</v>
+        <v>20.56375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.11</v>
       </c>
       <c r="M6" t="n">
-        <v>4.8275</v>
+        <v>8.18</v>
       </c>
       <c r="N6" t="n">
-        <v>16.865</v>
+        <v>19.2825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.07</v>
       </c>
       <c r="M7" t="n">
-        <v>4.39</v>
+        <v>6.79875</v>
       </c>
       <c r="N7" t="n">
-        <v>15.3375</v>
+        <v>14.555</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>3.42</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1775</v>
+        <v>3.470000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>10.82875</v>
+        <v>9.129999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1287500000000001</v>
+        <v>-0.1287499999999996</v>
       </c>
       <c r="N9" t="n">
         <v>5.19125</v>
@@ -1645,10 +1645,10 @@
         <v>2.04</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5162499999999999</v>
+        <v>0.5162500000000003</v>
       </c>
       <c r="N10" t="n">
-        <v>5.995</v>
+        <v>5.994999999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1772,10 +1772,10 @@
         <v>-1.87</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4475</v>
+        <v>0.4475000000000004</v>
       </c>
       <c r="N11" t="n">
-        <v>6.04375</v>
+        <v>6.043749999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1899,7 +1899,7 @@
         <v>-0.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7812499999999999</v>
+        <v>0.7812500000000003</v>
       </c>
       <c r="N12" t="n">
         <v>6.36</v>
@@ -9335,13 +9335,13 @@
         <v>12824</v>
       </c>
       <c r="D71" t="n">
-        <v>10390</v>
+        <v>10391</v>
       </c>
       <c r="E71" t="n">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="F71" t="n">
-        <v>18.98</v>
+        <v>18.97</v>
       </c>
       <c r="G71" t="n">
         <v>1228</v>
@@ -9367,7 +9367,7 @@
         <v>2.23625</v>
       </c>
       <c r="N71" t="n">
-        <v>19.69375</v>
+        <v>19.6925</v>
       </c>
       <c r="O71" t="n">
         <v>1</v>
@@ -9400,10 +9400,10 @@
         <v>0.5988372093023255</v>
       </c>
       <c r="Y71" t="n">
-        <v>5.210000000000001</v>
+        <v>5.199999999999999</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.3783587509077706</v>
+        <v>0.3776325344952796</v>
       </c>
       <c r="AA71" t="n">
         <v>0.1699999999999999</v>
@@ -9412,10 +9412,10 @@
         <v>0.06589147286821695</v>
       </c>
       <c r="AC71" t="n">
-        <v>-5.849999999999998</v>
+        <v>-5.859999999999999</v>
       </c>
       <c r="AD71" t="n">
-        <v>-0.2356020942408377</v>
+        <v>-0.2360048328634716</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -9462,13 +9462,13 @@
         <v>14511</v>
       </c>
       <c r="D72" t="n">
-        <v>11206</v>
+        <v>11205</v>
       </c>
       <c r="E72" t="n">
-        <v>3304</v>
+        <v>3305</v>
       </c>
       <c r="F72" t="n">
-        <v>22.77</v>
+        <v>22.78</v>
       </c>
       <c r="G72" t="n">
         <v>1910</v>
@@ -9527,10 +9527,10 @@
         <v>1.025454545454545</v>
       </c>
       <c r="Y72" t="n">
-        <v>3.789999999999999</v>
+        <v>3.810000000000002</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.1996838777660694</v>
+        <v>0.2008434370057988</v>
       </c>
       <c r="AA72" t="n">
         <v>3.56</v>
@@ -9539,10 +9539,10 @@
         <v>1.771144278606966</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.359999999999999</v>
+        <v>1.370000000000001</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.06352171882297997</v>
+        <v>0.06398879028491367</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -9654,10 +9654,10 @@
         <v>1.355475763016158</v>
       </c>
       <c r="Y73" t="n">
-        <v>25.6</v>
+        <v>25.59</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.124286341677646</v>
+        <v>1.123353819139596</v>
       </c>
       <c r="AA73" t="n">
         <v>12.08</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>38143</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22082</v>
+      </c>
+      <c r="E75" t="n">
+        <v>16061</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12765</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>33.47%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>963</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13729</v>
+      </c>
+      <c r="K75" t="n">
+        <v>10402</v>
+      </c>
+      <c r="L75" t="n">
+        <v>32.39</v>
+      </c>
+      <c r="M75" t="n">
+        <v>11.08125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.62375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.07787021630615643</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-13.59</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2439856373429085</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>10.77818181818182</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.219820769636268</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
